--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-device-use-statement-medicaldevice.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-device-use-statement-medicaldevice.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="342">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>DeviceUseStatement - Fr Device Use Statement Medical Device</t>
+    <t>DeviceUseStatement - Fr Dispositif médical</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -640,20 +640,298 @@
     <t>DeviceUseStatement.source</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document)
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson)
 </t>
   </si>
   <si>
+    <t>Dispensateur</t>
+  </si>
+  <si>
+    <t>Who reported the device was being used by the patient.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer</t>
+  </si>
+  <si>
+    <t>performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
     <t>Dispensateur: référence au professionnel de santé ou à l'organisation ayant initié ou dispensé le dispositif</t>
   </si>
   <si>
-    <t>Who reported the device was being used by the patient.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:type.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension.extension.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:type.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:type.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>PRF</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:reference.id</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:reference.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document)
+</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.url</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension:performer.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>DeviceUseStatement.source.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>DeviceUseStatement.device</t>
@@ -675,10 +953,6 @@
     <t>DeviceUseStatement.reasonCode</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Why device was used</t>
   </si>
   <si>
@@ -707,11 +981,8 @@
     <t>Indicates another resource whose existence justifies this DeviceUseStatement.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:resolve().code}
+    <t xml:space="preserve">value:resolve().code}
 </t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1132,11 +1403,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO27"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.1328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.22265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="64.3515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.80078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1145,7 +1416,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="160.10546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1160,10 +1431,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.76953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.4296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="31.3515625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3292,19 +3563,19 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>205</v>
@@ -3364,10 +3635,10 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -3376,34 +3647,34 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3419,18 +3690,20 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3467,19 +3740,19 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3491,22 +3764,22 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3514,9 +3787,11 @@
         <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
       </c>
@@ -3525,25 +3800,25 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3582,17 +3857,19 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3604,34 +3881,32 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>78</v>
       </c>
@@ -3649,16 +3924,16 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3709,55 +3984,53 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>78</v>
@@ -3766,16 +4039,16 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3814,19 +4087,19 @@
         <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3838,40 +4111,40 @@
         <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
@@ -3883,16 +4156,16 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3943,7 +4216,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3955,34 +4228,32 @@
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4000,16 +4271,16 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4060,42 +4331,42 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4106,7 +4377,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4115,21 +4386,19 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4153,46 +4422,46 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>78</v>
@@ -4204,15 +4473,15 @@
         <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4220,10 +4489,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -4235,22 +4504,24 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>251</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>78</v>
+        <v>229</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>78</v>
@@ -4292,38 +4563,3052 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH27" t="s" s="2">
+      <c r="B30" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
+      <c r="AI31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK27" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K46" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO27" t="s" s="2">
+      <c r="L46" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AC47" s="2"/>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO27">
+  <autoFilter ref="A1:AO53">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4333,7 +7618,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI26">
+  <conditionalFormatting sqref="A2:AI52">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-device-use-statement-medicaldevice.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-device-use-statement-medicaldevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
